--- a/data/trans_orig/IP16B05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B05-Provincia-trans_orig.xlsx
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
